--- a/data/trans_dic/IP44C$impuestos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,95</t>
+          <t>0,16; 4,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,02</t>
+          <t>0,17; 2,12</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,08</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,71</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>0,0; 8,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 4,63</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,17</t>
+          <t>0,34; 3,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,86</t>
+          <t>0,17; 3,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,66</t>
+          <t>0,46; 2,61</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,0</t>
+          <t>0,96; 7,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,69</t>
+          <t>0,59; 4,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,44</t>
+          <t>1,15; 4,55</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,13</t>
+          <t>1,12; 9,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,03</t>
+          <t>1,2; 7,69</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,92</t>
+          <t>1,11; 3,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,11</t>
+          <t>0,58; 1,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,19</t>
+          <t>1,01; 2,17</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>168; 4490</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2107</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>409; 5030</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6152</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5831</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3305</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5234</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5362</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2845</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>728; 7205</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>370; 8090</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1966; 11141</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2975</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6547</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1102; 8521</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>923; 7784</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3124; 12339</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2417</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4236</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>744; 6291</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 6049</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1624; 10412</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12105</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8372</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>20477</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>7180; 19613</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4249; 14328</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13834; 29922</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$impuestos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,36</t>
+          <t>0,32; 4,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,12</t>
+          <t>0,17; 2,13</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,5</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 8,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,2</t>
+          <t>0,0; 6,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,63</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,36</t>
+          <t>0,37; 3,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,8</t>
+          <t>0,24; 4,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,61</t>
+          <t>0,52; 2,51</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 7,44</t>
+          <t>1,05; 6,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,96</t>
+          <t>0,68; 5,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,55</t>
+          <t>1,13; 4,41</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,47</t>
+          <t>1,11; 9,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,78</t>
+          <t>0,0; 9,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,69</t>
+          <t>1,18; 6,95</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,04</t>
+          <t>1,11; 3,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,96</t>
+          <t>0,59; 2,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,17</t>
+          <t>0,99; 2,22</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>168; 4490</t>
+          <t>325; 4305</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2107</t>
+          <t>0; 2252</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>409; 5030</t>
+          <t>412; 5033</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6152</t>
+          <t>0; 4848</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5831</t>
+          <t>0; 5599</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3305</t>
+          <t>0; 4188</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5234</t>
+          <t>0; 3954</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5362</t>
+          <t>0; 6061</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>728; 7205</t>
+          <t>782; 7004</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>370; 8090</t>
+          <t>505; 9290</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1966; 11141</t>
+          <t>2241; 10727</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1102; 8521</t>
+          <t>1203; 7705</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>923; 7784</t>
+          <t>1062; 9150</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3124; 12339</t>
+          <t>3079; 11980</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>744; 6291</t>
+          <t>735; 6036</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6049</t>
+          <t>0; 6443</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1624; 10412</t>
+          <t>1592; 9410</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7180; 19613</t>
+          <t>7159; 19510</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4249; 14328</t>
+          <t>4300; 15009</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13834; 29922</t>
+          <t>13633; 30538</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$impuestos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,18</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,34; 4,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,13</t>
+          <t>0,17; 2,39</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,07</t>
+          <t>0,0; 9,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,19</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,24</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,27</t>
+          <t>0,26; 4,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,37</t>
+          <t>0,38; 3,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,51</t>
+          <t>0,58; 3,03</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,73</t>
+          <t>0,46; 4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,83</t>
+          <t>1,02; 7,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,41</t>
+          <t>1,26; 4,5</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,08</t>
+          <t>0,0; 8,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,35</t>
+          <t>1,03; 9,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,95</t>
+          <t>1,19; 6,85</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,03</t>
+          <t>0,57; 2,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,05</t>
+          <t>1,27; 3,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,22</t>
+          <t>1,05; 2,32</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>298</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1835</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>325; 4305</t>
+          <t>0; 1704</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2252</t>
+          <t>345; 4394</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>412; 5033</t>
+          <t>365; 5289</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1237</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4848</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6942</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5599</t>
+          <t>0; 6161</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>938</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>829</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1766</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4188</t>
+          <t>0; 5140</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3954</t>
+          <t>0; 4438</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6061</t>
+          <t>0; 6036</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5112</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>782; 7004</t>
+          <t>510; 8831</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>505; 9290</t>
+          <t>672; 6240</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2241; 10727</t>
+          <t>2157; 11285</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>6178</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1203; 7705</t>
+          <t>659; 6666</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1062; 9150</t>
+          <t>1165; 8384</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3079; 11980</t>
+          <t>3237; 11507</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>3940</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>735; 6036</t>
+          <t>0; 5800</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6443</t>
+          <t>699; 6273</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1592; 9410</t>
+          <t>1583; 9147</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>20068</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7159; 19510</t>
+          <t>3814; 14490</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4300; 15009</t>
+          <t>7721; 19372</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13633; 30538</t>
+          <t>13453; 29783</t>
         </is>
       </c>
     </row>
